--- a/output/pdf_financials_xlsx/GCC.xlsx
+++ b/output/pdf_financials_xlsx/GCC.xlsx
@@ -1944,13 +1944,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>2.008294</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>3.004831</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>3.444499</v>
       </c>
     </row>
     <row r="93">
@@ -3139,7 +3139,11 @@
           <t>Reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" s="5" t="n">
         <v>2.008294</v>
       </c>

--- a/output/pdf_financials_xlsx/GCC.xlsx
+++ b/output/pdf_financials_xlsx/GCC.xlsx
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.7e-05</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.268011</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.041505</v>
       </c>
     </row>
     <row r="35">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.7e-05</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.268011</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.041505</v>
       </c>
     </row>
     <row r="37">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.276163</v>
+        <v>0.276146</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.096536</v>
+        <v>0.828525</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.416056</v>
+        <v>1.374551</v>
       </c>
     </row>
     <row r="49">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
